--- a/Result/profitability/3607.xlsx
+++ b/Result/profitability/3607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.31625</v>
+        <v>0.3425</v>
       </c>
       <c r="N2" t="n">
-        <v>11.78375</v>
+        <v>12.54</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>3.29</v>
       </c>
       <c r="M3" t="n">
-        <v>0.74875</v>
+        <v>0.69875</v>
       </c>
       <c r="N3" t="n">
-        <v>15.155</v>
+        <v>15.4675</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>0.88375</v>
+        <v>0.93125</v>
       </c>
       <c r="N4" t="n">
-        <v>16.3175</v>
+        <v>17.41</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.88</v>
       </c>
       <c r="M5" t="n">
-        <v>1.16125</v>
+        <v>1.17125</v>
       </c>
       <c r="N5" t="n">
-        <v>17.20375</v>
+        <v>17.45625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.97</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2875</v>
+        <v>1.24</v>
       </c>
       <c r="N6" t="n">
-        <v>17.54125</v>
+        <v>17.60875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3975</v>
+        <v>1.40625</v>
       </c>
       <c r="N7" t="n">
-        <v>17.59125</v>
+        <v>18.3175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.3</v>
@@ -1391,16 +1391,16 @@
         <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>1.67</v>
+        <v>1.67125</v>
       </c>
       <c r="N8" t="n">
-        <v>18.62625</v>
+        <v>18.775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3607</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>790</v>
+      </c>
+      <c r="D74" t="n">
+        <v>677</v>
+      </c>
+      <c r="E74" t="n">
+        <v>113</v>
+      </c>
+      <c r="F74" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>6</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.04374999999999998</v>
+      </c>
+      <c r="N74" t="n">
+        <v>10.96375</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.09063214013709064</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.1642276422764226</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
